--- a/output/tabelas/3_1_despesa_por_orgao.xlsx
+++ b/output/tabelas/3_1_despesa_por_orgao.xlsx
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T21:10:18</t>
+          <t>2026-07-02T22:05:24</t>
         </is>
       </c>
     </row>
